--- a/test_data/real_data/metadata_Aragam_PEGSt000007.xlsx
+++ b/test_data/real_data/metadata_Aragam_PEGSt000007.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueji/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08290CE7-E9D1-2644-B123-F4E534251FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE90634-C4EB-4946-8A0E-E18C8CB1AB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="620" windowWidth="37120" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DatasetDescription" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="367">
   <si>
     <t>Free-text description of the phenotype under investigation.</t>
   </si>
@@ -722,10 +722,6 @@
   </si>
   <si>
     <t>https://www.gtexportal.org/home/datasets</t>
-  </si>
-  <si>
-    <t>adipose [subcutaneous, visceral omentum], adrenal gland, artery [aorta, coronary,
-tibial], liver and whole blood</t>
   </si>
   <si>
     <t>UK Biobank</t>
@@ -1015,12 +1011,6 @@
     <t>Adjusted P-value for the association between genotype and gene expression in visceral abdominal fat tissue from STARNET.</t>
   </si>
   <si>
-    <t>source_eqtl_gtex</t>
-  </si>
-  <si>
-    <t>source_eqtl_starnet</t>
-  </si>
-  <si>
     <t>Binary indicator of whether there is evidence of a significant eQTL association in any evaluated GTEx or STARNET tissue. A value of 1 indicates that at least one GTEx or STARNET tissue showed a significant eQTL association for the locus/gene; a value of 0 indicates that no significant eQTL association was identified in the evaluated tissues.</t>
   </si>
   <si>
@@ -1080,12 +1070,108 @@
   <si>
     <t>ECO_0000218</t>
   </si>
+  <si>
+    <t>source_eqtl_gtex_AdiposeVisceral</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_AdiposeVisceralOmentum</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_AdrenalGland</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_ArteryAorta</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_ArteryCoronary</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_ArteryTibial</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_Liver</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_WholeBlood</t>
+  </si>
+  <si>
+    <t>source_eqtl_gtex_AdiposeSubcutaneous</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_AOR</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_BLOOD</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_LIV</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_MAM</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_SF</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_SKLM</t>
+  </si>
+  <si>
+    <t>source_eqtl_starnet_VAF</t>
+  </si>
+  <si>
+    <t>Adipose Visceral</t>
+  </si>
+  <si>
+    <t>Adipose Visceral Omentum</t>
+  </si>
+  <si>
+    <t>Adipose Subcutaneous</t>
+  </si>
+  <si>
+    <t>Adrenal Gland</t>
+  </si>
+  <si>
+    <t>Artery Aorta</t>
+  </si>
+  <si>
+    <t>Artery Coronary</t>
+  </si>
+  <si>
+    <t>Artery Tibial</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>Whole Blood</t>
+  </si>
+  <si>
+    <t>Blood</t>
+  </si>
+  <si>
+    <t>Atherosclerotic Aortic Root</t>
+  </si>
+  <si>
+    <t>Atherosclerotic-lesion-free Internal Mammary Artery</t>
+  </si>
+  <si>
+    <t>Subcutaneous Fat</t>
+  </si>
+  <si>
+    <t>Skeletal Muscle</t>
+  </si>
+  <si>
+    <t>Visceral Abdominal Fat</t>
+  </si>
+  <si>
+    <t>Coronary artery disease</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1161,6 +1247,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1231,7 +1323,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1263,21 +1355,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1691,10 +1781,10 @@
         <v>26</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2012,9 +2102,9 @@
         <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="F4" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2337,7 +2427,7 @@
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>88</v>
@@ -2360,49 +2450,49 @@
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="12" t="str">
+      <c r="E5" s="5" t="str">
         <f>IF($D5="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D5,validation!$B$2:$B$24,0)),""))</f>
         <v>GWAS</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="12" t="str">
+      <c r="E6" s="5" t="str">
         <f>IF($D6="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D6,validation!$B$2:$B$24,0)),""))</f>
         <v>PROX</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="11" t="s">
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="15" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2410,679 +2500,679 @@
       <c r="A7" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="15"/>
+      <c r="D7" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="12" t="str">
+      <c r="E7" s="5" t="str">
         <f>IF($D7="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D7,validation!$B$2:$B$24,0)),""))</f>
         <v>FUNC</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C8" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C9" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="12" t="str">
+      <c r="E9" s="5" t="str">
         <f>IF($D9="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D9,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H9" s="11" t="s">
+      <c r="G9" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="H9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="C10" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="12" t="str">
+      <c r="E10" s="5" t="str">
         <f>IF($D10="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D10,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H10" s="11" t="s">
+      <c r="G10" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="12" t="str">
+      <c r="E11" s="5" t="str">
         <f>IF($D11="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D11,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H11" s="11" t="s">
+      <c r="G11" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="C12" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="12" t="str">
+      <c r="E12" s="5" t="str">
         <f>IF($D12="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D12,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H12" s="11" t="s">
+      <c r="G12" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="H12" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="12" t="str">
+      <c r="E13" s="5" t="str">
         <f>IF($D13="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D13,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H13" s="11" t="s">
+      <c r="G13" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="H13" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="C14" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="12" t="str">
+      <c r="E14" s="5" t="str">
         <f>IF($D14="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D14,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H14" s="11" t="s">
+      <c r="G14" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="C15" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="12" t="str">
+      <c r="E15" s="5" t="str">
         <f>IF($D15="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D15,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H15" s="11" t="s">
+      <c r="G15" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C16" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="12" t="str">
+      <c r="E16" s="5" t="str">
         <f>IF($D16="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D16,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H16" s="11" t="s">
+      <c r="G16" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C17" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="12" t="str">
+      <c r="E17" s="5" t="str">
         <f>IF($D17="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D17,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="H17" s="11" t="s">
+      <c r="G17" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J17" s="14"/>
-    </row>
-    <row r="18" spans="1:10" ht="96" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="12" t="str">
+      <c r="E18" s="5" t="str">
         <f>IF($D18="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D18,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H18" s="11" t="s">
+      <c r="G18" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="14"/>
-    </row>
-    <row r="19" spans="1:10" ht="80" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="12" t="str">
+      <c r="E19" s="5" t="str">
         <f>IF($D19="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D19,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H19" s="11" t="s">
+      <c r="G19" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="H19" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="1:10" ht="80" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" s="11" t="s">
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="12" t="str">
+      <c r="E20" s="5" t="str">
         <f>IF($D20="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D20,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H20" s="11" t="s">
+      <c r="G20" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="H20" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J20" s="14"/>
-    </row>
-    <row r="21" spans="1:10" ht="96" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="12" t="str">
+      <c r="E21" s="5" t="str">
         <f>IF($D21="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D21,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H21" s="11" t="s">
+      <c r="G21" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J21" s="14"/>
-    </row>
-    <row r="22" spans="1:10" ht="96" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="12" t="str">
+      <c r="E22" s="5" t="str">
         <f>IF($D22="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D22,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H22" s="11" t="s">
+      <c r="G22" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J22" s="14"/>
-    </row>
-    <row r="23" spans="1:10" ht="96" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="12" t="str">
+      <c r="E23" s="5" t="str">
         <f>IF($D23="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D23,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H23" s="11" t="s">
+      <c r="G23" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="24" spans="1:10" ht="96" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="12" t="str">
+      <c r="E24" s="5" t="str">
         <f>IF($D24="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D24,validation!$B$2:$B$24,0)),""))</f>
         <v>QTL</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="H24" s="11" t="s">
+      <c r="G24" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="J24" s="14"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="A25" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11" t="s">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="12" t="str">
+      <c r="E25" s="5" t="str">
         <f>IF($D25="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D25,validation!$B$2:$B$24,0)),""))</f>
         <v>DB</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="11" t="s">
+      <c r="H25" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="I25" s="16"/>
+      <c r="J25" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="224" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
+      <c r="B27" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E27" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F27" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="320" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14" t="s">
-        <v>335</v>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="A28" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11" t="s">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="12" t="str">
+      <c r="E28" s="5" t="str">
         <f>IF($D28="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D28,validation!$B$2:$B$24,0)),""))</f>
         <v>PERTURB</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="11" t="s">
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="A29" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11" t="s">
+      <c r="C29" s="15"/>
+      <c r="D29" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="12" t="str">
+      <c r="E29" s="5" t="str">
         <f>IF($D29="","",IFERROR(INDEX(validation!$A$2:$A$24,MATCH($D29,validation!$B$2:$B$24,0)),""))</f>
         <v>PERTURB</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11" t="s">
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="15" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5097,95 +5187,86 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="D6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="5">
+        <v>4</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="D4" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="D5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" s="12">
-        <v>4</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -5399,7 +5480,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -5414,7 +5495,7 @@
     <col min="10" max="10" width="25.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
     <col min="12" max="12" width="28.6640625" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" customWidth="1"/>
     <col min="14" max="14" width="14.6640625" customWidth="1"/>
     <col min="15" max="15" width="15.6640625" customWidth="1"/>
     <col min="16" max="16" width="36.6640625" customWidth="1"/>
@@ -5561,7 +5642,7 @@
         <v>214</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>215</v>
@@ -5595,127 +5676,638 @@
       </c>
     </row>
     <row r="4" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>320</v>
+      <c r="A4" t="s">
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I4" t="s">
-        <v>222</v>
-      </c>
-      <c r="J4" t="s">
         <v>227</v>
       </c>
-      <c r="K4" t="s">
-        <v>222</v>
-      </c>
-      <c r="N4" t="s">
-        <v>220</v>
-      </c>
-      <c r="P4" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>336</v>
+      <c r="G4" t="s">
+        <v>228</v>
+      </c>
+      <c r="R4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5">
+        <v>10.1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>103</v>
+      <c r="A6" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" t="s">
-        <v>229</v>
-      </c>
-      <c r="R6" t="s">
-        <v>230</v>
+        <v>231</v>
+      </c>
+      <c r="D6">
+        <v>2019</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7">
-        <v>10.1</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>273</v>
+        <v>232</v>
+      </c>
+      <c r="D7" s="13">
+        <v>43988</v>
+      </c>
+      <c r="E7" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>110</v>
+      <c r="A8" s="15" t="s">
+        <v>343</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D8">
-        <v>2019</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>115</v>
+        <v>209</v>
+      </c>
+      <c r="D8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="K8" t="s">
+        <v>222</v>
+      </c>
+      <c r="N8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>335</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D9" s="17">
-        <v>43988</v>
+        <v>209</v>
+      </c>
+      <c r="D9" t="s">
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>226</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="K9" t="s">
+        <v>222</v>
+      </c>
+      <c r="N9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="K10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="K11" t="s">
+        <v>222</v>
+      </c>
+      <c r="N11" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="B12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="K12" t="s">
+        <v>222</v>
+      </c>
+      <c r="N12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P12" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="K13" t="s">
+        <v>222</v>
+      </c>
+      <c r="N13" t="s">
+        <v>220</v>
+      </c>
+      <c r="P13" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="K14" t="s">
+        <v>222</v>
+      </c>
+      <c r="N14" t="s">
+        <v>220</v>
+      </c>
+      <c r="P14" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" t="s">
+        <v>226</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="K15" t="s">
+        <v>222</v>
+      </c>
+      <c r="N15" t="s">
+        <v>220</v>
+      </c>
+      <c r="P15" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="K16" t="s">
+        <v>222</v>
+      </c>
+      <c r="N16" t="s">
+        <v>220</v>
+      </c>
+      <c r="P16" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J17" t="s">
+        <v>361</v>
+      </c>
+      <c r="K17" t="s">
+        <v>222</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N17" t="s">
+        <v>220</v>
+      </c>
+      <c r="O17" s="11"/>
+      <c r="P17" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>223</v>
+      </c>
+      <c r="R17" s="11"/>
+    </row>
+    <row r="18" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J18" t="s">
+        <v>360</v>
+      </c>
+      <c r="K18" t="s">
+        <v>222</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N18" t="s">
+        <v>220</v>
+      </c>
+      <c r="O18" s="11"/>
+      <c r="P18" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>223</v>
+      </c>
+      <c r="R18" s="11"/>
+    </row>
+    <row r="19" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J19" t="s">
+        <v>358</v>
+      </c>
+      <c r="K19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N19" t="s">
+        <v>220</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>223</v>
+      </c>
+      <c r="R19" s="11"/>
+    </row>
+    <row r="20" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" t="s">
+        <v>362</v>
+      </c>
+      <c r="K20" t="s">
+        <v>222</v>
+      </c>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N20" t="s">
+        <v>220</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>223</v>
+      </c>
+      <c r="R20" s="11"/>
+    </row>
+    <row r="21" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" t="s">
+        <v>363</v>
+      </c>
+      <c r="K21" t="s">
+        <v>222</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N21" t="s">
+        <v>220</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>223</v>
+      </c>
+      <c r="R21" s="11"/>
+    </row>
+    <row r="22" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>349</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J22" t="s">
+        <v>364</v>
+      </c>
+      <c r="K22" t="s">
+        <v>222</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N22" t="s">
+        <v>220</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>223</v>
+      </c>
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J23" t="s">
+        <v>365</v>
+      </c>
+      <c r="K23" t="s">
+        <v>222</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="N23" t="s">
+        <v>220</v>
+      </c>
+      <c r="O23" s="11"/>
+      <c r="P23" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>223</v>
+      </c>
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:18" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5883,25 +6475,29 @@
     <row r="197" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="198" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="199" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4 N6:N201" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4:N199" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"healthy,disease"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4 R6:R201" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4:R16 R24:R199" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"male,female,mixed,unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S4 S6:S201" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S4:S199" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>"PATO_0000383,PATO_0000384,PATO_0001894"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" xr:uid="{DF453A78-73CF-7B4F-BCA0-2AD1F3B0C58B}"/>
-    <hyperlink ref="E8" r:id="rId2" xr:uid="{2550F63D-D44F-9F46-89C8-2DEB07501572}"/>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{DF453A78-73CF-7B4F-BCA0-2AD1F3B0C58B}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{2550F63D-D44F-9F46-89C8-2DEB07501572}"/>
     <hyperlink ref="E3" r:id="rId3" xr:uid="{16664FD4-CD5D-3D4F-B119-866D0CD400D8}"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://doi.org/10.1126/science.aad6970" xr:uid="{FE665AED-DE50-BD47-AA31-C425F1331E02}"/>
+    <hyperlink ref="G17" r:id="rId4" display="https://doi.org/10.1126/science.aad6970" xr:uid="{8A9B5D6A-335A-6045-B88A-06D2A8577605}"/>
+    <hyperlink ref="G18" r:id="rId5" display="https://doi.org/10.1126/science.aad6970" xr:uid="{C6B57537-AD41-1F43-B129-B229A1B864B1}"/>
+    <hyperlink ref="G19" r:id="rId6" display="https://doi.org/10.1126/science.aad6970" xr:uid="{099AB1CD-407F-9244-B42F-455E2DC32E98}"/>
+    <hyperlink ref="G20" r:id="rId7" display="https://doi.org/10.1126/science.aad6970" xr:uid="{CFB2B7BD-2093-694D-9863-5E861A59694B}"/>
+    <hyperlink ref="G21" r:id="rId8" display="https://doi.org/10.1126/science.aad6970" xr:uid="{A9520069-E4F0-7A46-83FA-DBFD36FF6CA7}"/>
+    <hyperlink ref="G22" r:id="rId9" display="https://doi.org/10.1126/science.aad6970" xr:uid="{7C5DADCF-DE3C-0247-A449-0A1DDF3EC356}"/>
+    <hyperlink ref="G23" r:id="rId10" display="https://doi.org/10.1126/science.aad6970" xr:uid="{4CBA8FF1-31F2-444E-B1C7-AE09E37A23E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5924,31 +6520,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -5956,25 +6552,25 @@
         <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>76</v>
@@ -5985,46 +6581,46 @@
         <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6032,16 +6628,16 @@
         <v>90</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D5" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6049,13 +6645,13 @@
         <v>99</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6063,13 +6659,13 @@
         <v>104</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6077,10 +6673,10 @@
         <v>107</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6088,16 +6684,16 @@
         <v>169</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6105,27 +6701,27 @@
         <v>174</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
